--- a/10반.xlsx
+++ b/10반.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>CIP2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>CIP3</t>
         </is>
@@ -453,10 +458,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>김선민</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>활동실2</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>활동실2</t>
         </is>

--- a/10반.xlsx
+++ b/10반.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,28 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>활동실2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>21011</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>김해환</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>활동실2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>활동실2</t>
         </is>

--- a/10반.xlsx
+++ b/10반.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김선민</t>
+          <t>고승한</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -475,22 +475,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>김선민</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>활동실2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>활동실2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>21011</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>김해환</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>활동실2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>활동실2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>21020</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>유은찬</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>자습실1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>자습실1</t>
         </is>
       </c>
     </row>

--- a/10반.xlsx
+++ b/10반.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,12 +485,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>활동실2</t>
+          <t>활동실3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>활동실2</t>
+          <t>활동실3</t>
         </is>
       </c>
     </row>
@@ -535,6 +535,28 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>자습실1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>21026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>이주표</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>자습실5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>자습실5</t>
         </is>
       </c>
     </row>

--- a/10반.xlsx
+++ b/10반.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>자습실5</t>
+          <t>수행실1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>자습실5</t>
+          <t>수행실1</t>
         </is>
       </c>
     </row>

--- a/10반.xlsx
+++ b/10반.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,86 +475,152 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김선민</t>
+          <t>김민성</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>활동실3</t>
+          <t>자습실2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>활동실3</t>
+          <t>자습실2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김해환</t>
+          <t>김선민</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>활동실2</t>
+          <t>활동실3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>활동실2</t>
+          <t>활동실3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21020</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>유은찬</t>
+          <t>김해환</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>자습실1</t>
+          <t>활동실2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>자습실1</t>
+          <t>활동실2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>유은찬</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>자습실1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>자습실1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>21021</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>이나운</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>활동실2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>활동실2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>21024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>이성민</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>수행실1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>수행실1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>21026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>이주표</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>수행실1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>수행실1</t>
         </is>

--- a/10반.xlsx
+++ b/10반.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,176 +453,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>고승한</t>
+          <t>김선민</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>활동실2</t>
+          <t>자습실4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>활동실2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>21005</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>김민성</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>자습실2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>자습실2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>21008</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>김선민</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>활동실3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>활동실3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>21011</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>김해환</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>활동실2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>활동실2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>21020</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>유은찬</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>자습실1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>자습실1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>21021</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>이나운</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>활동실2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>활동실2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>이성민</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>수행실1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>수행실1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>21026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>이주표</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>수행실1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>수행실1</t>
+          <t>자습실4</t>
         </is>
       </c>
     </row>
